--- a/docs/demo/cedvel_sehvli.xlsx
+++ b/docs/demo/cedvel_sehvli.xlsx
@@ -425,7 +425,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1">
-        <v>46321.0</v>
+        <v>46300.0</v>
       </c>
       <c r="B2" s="2">
         <v>0.79166666666667</v>
@@ -461,7 +461,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1">
-        <v>46323.0</v>
+        <v>46302.0</v>
       </c>
       <c r="B4" s="2">
         <v>0.875</v>
@@ -479,7 +479,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1">
-        <v>46321.0</v>
+        <v>46300.0</v>
       </c>
       <c r="B5" s="2">
         <v>0.83333333333333</v>
